--- a/simulations/correction_peat_market/all_dig_ss_inv.xlsx
+++ b/simulations/correction_peat_market/all_dig_ss_inv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B2C87B-85FB-4D65-ACA2-266AFBA43103}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163C69B0-1F78-49B5-8179-D9650C3265C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3742,30 +3742,6 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="results"/>
-      <sheetName val="CC_contribution"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="AG2" t="str">
-            <v>EQssC</v>
-          </cell>
-          <cell r="AH2" t="str">
-            <v>HHssC</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
       <sheetName val="Feuil1"/>
       <sheetName val="Feuil2"/>
     </sheetNames>
@@ -3816,7 +3792,29 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="results"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="AG2" t="str">
+            <v>EQssC</v>
+          </cell>
+          <cell r="AH2" t="str">
+            <v>HHssC</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4583,7 +4581,7 @@
         <v>426.04896000000002</v>
       </c>
       <c r="AS3">
-        <f t="shared" ref="AS3:AV5" si="0">$AK$12*$AK$13*AL3/100</f>
+        <f t="shared" ref="AS3:AU5" si="0">$AK$12*$AK$13*AL3/100</f>
         <v>516.84101999999996</v>
       </c>
       <c r="AT3">
@@ -4598,57 +4596,57 @@
         <v>48</v>
       </c>
       <c r="AX3" s="4">
-        <f>AR3*[2]Feuil1!$I$6</f>
+        <f>AR3*[1]Feuil1!$I$6</f>
         <v>14598.36355587391</v>
       </c>
       <c r="AY3" s="4">
-        <f>AS3*[2]Feuil1!$I$7</f>
+        <f>AS3*[1]Feuil1!$I$7</f>
         <v>18307.190713916687</v>
       </c>
       <c r="AZ3" s="4">
-        <f>AT3*[2]Feuil1!$I$9</f>
+        <f>AT3*[1]Feuil1!$I$9</f>
         <v>0</v>
       </c>
       <c r="BA3" s="4">
-        <f>AU3*[2]Feuil1!$I$10</f>
+        <f>AU3*[1]Feuil1!$I$10</f>
         <v>376242.62027969374</v>
       </c>
       <c r="BC3" t="s">
         <v>48</v>
       </c>
       <c r="BD3" s="4">
-        <f>AR3*[2]Feuil1!$J$6</f>
+        <f>AR3*[1]Feuil1!$J$6</f>
         <v>19398.615198578285</v>
       </c>
       <c r="BE3" s="4">
-        <f>AS3*[2]Feuil1!$J$7</f>
+        <f>AS3*[1]Feuil1!$J$7</f>
         <v>24968.637769751538</v>
       </c>
       <c r="BF3" s="4">
-        <f>AT3*[2]Feuil1!$J$9</f>
+        <f>AT3*[1]Feuil1!$J$9</f>
         <v>0</v>
       </c>
       <c r="BG3" s="4">
-        <f>AU3*[2]Feuil1!$J$10</f>
+        <f>AU3*[1]Feuil1!$J$10</f>
         <v>174134.9227763011</v>
       </c>
       <c r="BJ3" t="s">
         <v>48</v>
       </c>
       <c r="BK3" s="4">
-        <f>AR3*[2]Feuil1!$K$6</f>
+        <f>AR3*[1]Feuil1!$K$6</f>
         <v>6.5358067728752731E-2</v>
       </c>
       <c r="BL3" s="4">
-        <f>AS3*[2]Feuil1!$K$7</f>
+        <f>AS3*[1]Feuil1!$K$7</f>
         <v>0.13734219331420006</v>
       </c>
       <c r="BM3" s="4">
-        <f>AT3*[2]Feuil1!$K$9</f>
+        <f>AT3*[1]Feuil1!$K$9</f>
         <v>0</v>
       </c>
       <c r="BN3" s="4">
-        <f>AU3*[2]Feuil1!$K$10</f>
+        <f>AU3*[1]Feuil1!$K$10</f>
         <v>1.4318302299145982</v>
       </c>
     </row>
@@ -4738,57 +4736,57 @@
         <v>38</v>
       </c>
       <c r="AX4" s="4">
-        <f>AR4*[2]Feuil1!$I$6</f>
+        <f>AR4*[1]Feuil1!$I$6</f>
         <v>14598.36355587391</v>
       </c>
       <c r="AY4" s="4">
-        <f>AS4*[2]Feuil1!$I$7</f>
+        <f>AS4*[1]Feuil1!$I$7</f>
         <v>0</v>
       </c>
       <c r="AZ4" s="4">
-        <f>AT4*[2]Feuil1!$I$9</f>
+        <f>AT4*[1]Feuil1!$I$9</f>
         <v>320084.04960827704</v>
       </c>
       <c r="BA4" s="4">
-        <f>AU4*[2]Feuil1!$I$10</f>
+        <f>AU4*[1]Feuil1!$I$10</f>
         <v>0</v>
       </c>
       <c r="BC4" t="s">
         <v>38</v>
       </c>
       <c r="BD4" s="4">
-        <f>AR4*[2]Feuil1!$J$6</f>
+        <f>AR4*[1]Feuil1!$J$6</f>
         <v>19398.615198578285</v>
       </c>
       <c r="BE4" s="4">
-        <f>AS4*[2]Feuil1!$J$7</f>
+        <f>AS4*[1]Feuil1!$J$7</f>
         <v>0</v>
       </c>
       <c r="BF4" s="4">
-        <f>AT4*[2]Feuil1!$J$9</f>
+        <f>AT4*[1]Feuil1!$J$9</f>
         <v>122827.41842358082</v>
       </c>
       <c r="BG4" s="4">
-        <f>AU4*[2]Feuil1!$J$10</f>
+        <f>AU4*[1]Feuil1!$J$10</f>
         <v>0</v>
       </c>
       <c r="BJ4" t="s">
         <v>38</v>
       </c>
       <c r="BK4" s="4">
-        <f>AR4*[2]Feuil1!$K$6</f>
+        <f>AR4*[1]Feuil1!$K$6</f>
         <v>6.5358067728752731E-2</v>
       </c>
       <c r="BL4" s="4">
-        <f>AS4*[2]Feuil1!$K$7</f>
+        <f>AS4*[1]Feuil1!$K$7</f>
         <v>0</v>
       </c>
       <c r="BM4" s="4">
-        <f>AT4*[2]Feuil1!$K$9</f>
+        <f>AT4*[1]Feuil1!$K$9</f>
         <v>1.3995133906359016</v>
       </c>
       <c r="BN4" s="4">
-        <f>AU4*[2]Feuil1!$K$10</f>
+        <f>AU4*[1]Feuil1!$K$10</f>
         <v>0</v>
       </c>
     </row>
@@ -4878,57 +4876,57 @@
         <v>39</v>
       </c>
       <c r="AX5" s="4">
-        <f>AR5*[2]Feuil1!$I$6</f>
+        <f>AR5*[1]Feuil1!$I$6</f>
         <v>14598.36355587391</v>
       </c>
       <c r="AY5" s="4">
-        <f>AS5*[2]Feuil1!$I$7</f>
+        <f>AS5*[1]Feuil1!$I$7</f>
         <v>0</v>
       </c>
       <c r="AZ5" s="4">
-        <f>AT5*[2]Feuil1!$I$9</f>
+        <f>AT5*[1]Feuil1!$I$9</f>
         <v>320084.04960827704</v>
       </c>
       <c r="BA5" s="4">
-        <f>AU5*[2]Feuil1!$I$10</f>
+        <f>AU5*[1]Feuil1!$I$10</f>
         <v>0</v>
       </c>
       <c r="BC5" t="s">
         <v>39</v>
       </c>
       <c r="BD5" s="4">
-        <f>AR5*[2]Feuil1!$J$6</f>
+        <f>AR5*[1]Feuil1!$J$6</f>
         <v>19398.615198578285</v>
       </c>
       <c r="BE5" s="4">
-        <f>AS5*[2]Feuil1!$J$7</f>
+        <f>AS5*[1]Feuil1!$J$7</f>
         <v>0</v>
       </c>
       <c r="BF5" s="4">
-        <f>AT5*[2]Feuil1!$J$9</f>
+        <f>AT5*[1]Feuil1!$J$9</f>
         <v>122827.41842358082</v>
       </c>
       <c r="BG5" s="4">
-        <f>AU5*[2]Feuil1!$J$10</f>
+        <f>AU5*[1]Feuil1!$J$10</f>
         <v>0</v>
       </c>
       <c r="BJ5" t="s">
         <v>39</v>
       </c>
       <c r="BK5" s="4">
-        <f>AR5*[2]Feuil1!$K$6</f>
+        <f>AR5*[1]Feuil1!$K$6</f>
         <v>6.5358067728752731E-2</v>
       </c>
       <c r="BL5" s="4">
-        <f>AS5*[2]Feuil1!$K$7</f>
+        <f>AS5*[1]Feuil1!$K$7</f>
         <v>0</v>
       </c>
       <c r="BM5" s="4">
-        <f>AT5*[2]Feuil1!$K$9</f>
+        <f>AT5*[1]Feuil1!$K$9</f>
         <v>1.3995133906359016</v>
       </c>
       <c r="BN5" s="4">
-        <f>AU5*[2]Feuil1!$K$10</f>
+        <f>AU5*[1]Feuil1!$K$10</f>
         <v>0</v>
       </c>
     </row>
@@ -5363,7 +5361,7 @@
         <v>58</v>
       </c>
       <c r="C2" t="str">
-        <f>[1]results!AG2</f>
+        <f>[2]results!AG2</f>
         <v>EQssC</v>
       </c>
       <c r="D2" t="s">
@@ -5376,7 +5374,7 @@
         <v>60</v>
       </c>
       <c r="H2" t="str">
-        <f>[1]results!AH2</f>
+        <f>[2]results!AH2</f>
         <v>HHssC</v>
       </c>
       <c r="I2" t="s">

--- a/simulations/correction_peat_market/all_dig_ss_inv.xlsx
+++ b/simulations/correction_peat_market/all_dig_ss_inv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163C69B0-1F78-49B5-8179-D9650C3265C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD1E8F2-BB08-4E9B-A15E-9BFFA1D63B9A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
